--- a/echelle.xlsx
+++ b/echelle.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkichenin\Desktop\Observatoire\4.ANRU\NPNRU_RSTUDIO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04DFE35A-BF76-41EB-BB40-DC31046AD386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639BF0F7-ACAC-4D23-ACFC-9A0105A7858D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{37DD0267-8834-4621-BFC1-3630451AA18D}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{37DD0267-8834-4621-BFC1-3630451AA18D}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>MOA</t>
   </si>
@@ -48,21 +48,6 @@
   </si>
   <si>
     <t>% de réalisation</t>
-  </si>
-  <si>
-    <t>Ville de Saint-Benoît</t>
-  </si>
-  <si>
-    <t>SIDR</t>
-  </si>
-  <si>
-    <t>SHLMR</t>
-  </si>
-  <si>
-    <t>SEMAC</t>
-  </si>
-  <si>
-    <t>CIREST</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -173,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,18 +168,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -539,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42C8AD98-8C5C-4D1B-97F1-81A2F17340B7}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
@@ -553,7 +526,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -564,82 +537,12 @@
         <v>3</v>
       </c>
       <c r="B2" s="4">
-        <v>12165</v>
+        <v>34025</v>
       </c>
       <c r="C2" s="5">
-        <v>0</v>
+        <v>12283.5</v>
       </c>
       <c r="D2" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4">
-        <v>9934</v>
-      </c>
-      <c r="C3" s="4">
-        <v>2147</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0.216</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="4">
-        <v>8164</v>
-      </c>
-      <c r="C4" s="5">
-        <v>4099</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0.502</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4">
-        <v>2466</v>
-      </c>
-      <c r="C5" s="4">
-        <v>2711</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1.099</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4">
-        <v>1296</v>
-      </c>
-      <c r="C6" s="5">
-        <v>3326.5</v>
-      </c>
-      <c r="D6" s="7">
-        <v>2.5659999999999998</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" thickBot="1">
-      <c r="A7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="8">
-        <v>34025</v>
-      </c>
-      <c r="C7" s="9">
-        <v>12283.5</v>
-      </c>
-      <c r="D7" s="10">
         <v>0.36099999999999999</v>
       </c>
     </row>
